--- a/Excel/Excel_Dashboard_2/Data_Uncleaned.xlsx
+++ b/Excel/Excel_Dashboard_2/Data_Uncleaned.xlsx
@@ -2,28 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Weekend\Excel\Excel_Dashboard_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FC99E5-C9CF-4243-927B-2798F9C04DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7172E62D-69A5-4B05-BDD1-4F54E4C8BC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot 1" sheetId="3" r:id="rId1"/>
     <sheet name="Pivot 2" sheetId="4" r:id="rId2"/>
-    <sheet name="Production Dataset" sheetId="1" r:id="rId3"/>
+    <sheet name="Pivot 3" sheetId="6" r:id="rId3"/>
+    <sheet name="Production Dataset" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Production Dataset'!$A$1:$J$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Production Dataset'!$A$1:$J$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
-    <pivotCache cacheId="9" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="51">
   <si>
     <t>ProductionID</t>
   </si>
@@ -154,13 +155,58 @@
   <si>
     <t>Total Production cost by product type</t>
   </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Sum of UnitsProduced</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -199,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -207,48 +253,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -256,6 +279,7 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FF808080"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCC99"/>
       <color rgb="FFCCFFCC"/>
@@ -919,19 +943,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1308,6 +1320,706 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Data_Uncleaned.xlsx]Pivot 3!PivotTable3</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1" i="1" u="sng">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Number of units produced in each month</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d>
+            <a:contourClr>
+              <a:schemeClr val="bg2"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="3.770739064856712E-3"/>
+              <c:y val="-7.4990626171728539E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:line3DChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot 3'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d>
+                <a:contourClr>
+                  <a:schemeClr val="bg2"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-1237-498A-ABCD-467F00CD1670}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.770739064856712E-3"/>
+                  <c:y val="-7.4990626171728539E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-1237-498A-ABCD-467F00CD1670}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Pivot 3'!$A$4:$A$19</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="13"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Sep</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2023</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>2024</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot 3'!$B$4:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>771</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4803</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2494</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4127</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3875</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1528</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1684</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3537</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1379</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1237-498A-ABCD-467F00CD1670}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1191456976"/>
+        <c:axId val="1191465136"/>
+        <c:axId val="1438982608"/>
+      </c:line3DChart>
+      <c:catAx>
+        <c:axId val="1191456976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1191465136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1191465136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1191456976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:serAx>
+        <c:axId val="1438982608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1191465136"/>
+        <c:crosses val="autoZero"/>
+      </c:serAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1349,6 +2061,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2436,6 +3188,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="307">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2518,6 +3786,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9495F7F-8735-0E6F-0A61-4A93CB0EFB49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ADMIN" refreshedDate="45892.62998888889" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{4259D648-941E-42F3-9B2E-42A72C5A37AD}">
   <cacheSource type="worksheet">
@@ -2579,12 +3888,113 @@
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:K121" sheet="Production Dataset"/>
   </cacheSource>
-  <cacheFields count="11">
+  <cacheFields count="14">
     <cacheField name="ProductionID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="120"/>
     </cacheField>
     <cacheField name="ProductionDate" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-22T00:00:00" maxDate="2024-09-15T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-09-22T00:00:00" maxDate="2024-09-15T00:00:00" count="99">
+        <d v="2023-09-22T00:00:00"/>
+        <d v="2023-09-24T00:00:00"/>
+        <d v="2023-09-28T00:00:00"/>
+        <d v="2023-10-01T00:00:00"/>
+        <d v="2023-10-08T00:00:00"/>
+        <d v="2023-10-15T00:00:00"/>
+        <d v="2023-10-16T00:00:00"/>
+        <d v="2023-10-17T00:00:00"/>
+        <d v="2023-10-18T00:00:00"/>
+        <d v="2023-10-22T00:00:00"/>
+        <d v="2023-10-29T00:00:00"/>
+        <d v="2023-10-31T00:00:00"/>
+        <d v="2023-11-02T00:00:00"/>
+        <d v="2023-11-03T00:00:00"/>
+        <d v="2023-11-04T00:00:00"/>
+        <d v="2023-11-05T00:00:00"/>
+        <d v="2023-11-10T00:00:00"/>
+        <d v="2023-11-13T00:00:00"/>
+        <d v="2023-11-19T00:00:00"/>
+        <d v="2023-11-21T00:00:00"/>
+        <d v="2023-11-22T00:00:00"/>
+        <d v="2023-11-24T00:00:00"/>
+        <d v="2023-11-26T00:00:00"/>
+        <d v="2023-12-04T00:00:00"/>
+        <d v="2023-12-13T00:00:00"/>
+        <d v="2023-12-14T00:00:00"/>
+        <d v="2023-12-17T00:00:00"/>
+        <d v="2023-12-22T00:00:00"/>
+        <d v="2023-12-26T00:00:00"/>
+        <d v="2023-12-29T00:00:00"/>
+        <d v="2024-01-01T00:00:00"/>
+        <d v="2024-01-02T00:00:00"/>
+        <d v="2024-01-03T00:00:00"/>
+        <d v="2024-01-05T00:00:00"/>
+        <d v="2024-01-08T00:00:00"/>
+        <d v="2024-01-13T00:00:00"/>
+        <d v="2024-01-14T00:00:00"/>
+        <d v="2024-01-16T00:00:00"/>
+        <d v="2024-01-18T00:00:00"/>
+        <d v="2024-01-27T00:00:00"/>
+        <d v="2024-02-07T00:00:00"/>
+        <d v="2024-02-08T00:00:00"/>
+        <d v="2024-02-13T00:00:00"/>
+        <d v="2024-02-17T00:00:00"/>
+        <d v="2024-02-25T00:00:00"/>
+        <d v="2024-02-26T00:00:00"/>
+        <d v="2024-02-28T00:00:00"/>
+        <d v="2024-03-05T00:00:00"/>
+        <d v="2024-03-06T00:00:00"/>
+        <d v="2024-03-10T00:00:00"/>
+        <d v="2024-03-13T00:00:00"/>
+        <d v="2024-03-18T00:00:00"/>
+        <d v="2024-03-19T00:00:00"/>
+        <d v="2024-03-20T00:00:00"/>
+        <d v="2024-03-21T00:00:00"/>
+        <d v="2024-03-23T00:00:00"/>
+        <d v="2024-03-26T00:00:00"/>
+        <d v="2024-03-27T00:00:00"/>
+        <d v="2024-03-29T00:00:00"/>
+        <d v="2024-03-30T00:00:00"/>
+        <d v="2024-04-01T00:00:00"/>
+        <d v="2024-04-08T00:00:00"/>
+        <d v="2024-04-10T00:00:00"/>
+        <d v="2024-04-16T00:00:00"/>
+        <d v="2024-04-25T00:00:00"/>
+        <d v="2024-04-28T00:00:00"/>
+        <d v="2024-04-30T00:00:00"/>
+        <d v="2024-05-08T00:00:00"/>
+        <d v="2024-05-10T00:00:00"/>
+        <d v="2024-05-12T00:00:00"/>
+        <d v="2024-05-15T00:00:00"/>
+        <d v="2024-05-20T00:00:00"/>
+        <d v="2024-06-01T00:00:00"/>
+        <d v="2024-06-06T00:00:00"/>
+        <d v="2024-06-08T00:00:00"/>
+        <d v="2024-06-10T00:00:00"/>
+        <d v="2024-06-14T00:00:00"/>
+        <d v="2024-06-15T00:00:00"/>
+        <d v="2024-06-21T00:00:00"/>
+        <d v="2024-06-22T00:00:00"/>
+        <d v="2024-06-24T00:00:00"/>
+        <d v="2024-06-26T00:00:00"/>
+        <d v="2024-06-29T00:00:00"/>
+        <d v="2024-07-05T00:00:00"/>
+        <d v="2024-07-16T00:00:00"/>
+        <d v="2024-07-24T00:00:00"/>
+        <d v="2024-07-31T00:00:00"/>
+        <d v="2024-08-02T00:00:00"/>
+        <d v="2024-08-04T00:00:00"/>
+        <d v="2024-08-06T00:00:00"/>
+        <d v="2024-08-07T00:00:00"/>
+        <d v="2024-08-16T00:00:00"/>
+        <d v="2024-08-17T00:00:00"/>
+        <d v="2024-08-23T00:00:00"/>
+        <d v="2024-08-26T00:00:00"/>
+        <d v="2024-08-28T00:00:00"/>
+        <d v="2024-09-08T00:00:00"/>
+        <d v="2024-09-09T00:00:00"/>
+        <d v="2024-09-14T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="13"/>
     </cacheField>
     <cacheField name="Region" numFmtId="0">
       <sharedItems/>
@@ -2618,6 +4028,51 @@
     <cacheField name="Cost of 1 unit" numFmtId="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.3287671232876712" maxValue="1115.4509803921569"/>
     </cacheField>
+    <cacheField name="Months (ProductionDate)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="months" startDate="2023-09-22T00:00:00" endDate="2024-09-15T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;9/22/2023"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;9/15/2024"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Quarters (ProductionDate)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="quarters" startDate="2023-09-22T00:00:00" endDate="2024-09-15T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;9/22/2023"/>
+          <s v="Qtr1"/>
+          <s v="Qtr2"/>
+          <s v="Qtr3"/>
+          <s v="Qtr4"/>
+          <s v="&gt;9/15/2024"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Years (ProductionDate)" numFmtId="0" databaseField="0">
+      <fieldGroup base="1">
+        <rangePr groupBy="years" startDate="2023-09-22T00:00:00" endDate="2024-09-15T00:00:00"/>
+        <groupItems count="4">
+          <s v="&lt;9/22/2023"/>
+          <s v="2023"/>
+          <s v="2024"/>
+          <s v="&gt;9/15/2024"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -4076,7 +5531,7 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="120">
   <r>
     <n v="48"/>
-    <d v="2023-09-22T00:00:00"/>
+    <x v="0"/>
     <s v="North"/>
     <s v="Jane Smith"/>
     <x v="0"/>
@@ -4089,7 +5544,7 @@
   </r>
   <r>
     <n v="56"/>
-    <d v="2023-09-24T00:00:00"/>
+    <x v="1"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4102,7 +5557,7 @@
   </r>
   <r>
     <n v="74"/>
-    <d v="2023-09-28T00:00:00"/>
+    <x v="2"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="0"/>
@@ -4115,7 +5570,7 @@
   </r>
   <r>
     <n v="30"/>
-    <d v="2023-10-01T00:00:00"/>
+    <x v="3"/>
     <s v="West"/>
     <s v="Emily Davis"/>
     <x v="1"/>
@@ -4128,7 +5583,7 @@
   </r>
   <r>
     <n v="46"/>
-    <d v="2023-10-08T00:00:00"/>
+    <x v="4"/>
     <s v="West"/>
     <s v="Andrew Blue"/>
     <x v="1"/>
@@ -4141,7 +5596,7 @@
   </r>
   <r>
     <n v="35"/>
-    <d v="2023-10-15T00:00:00"/>
+    <x v="5"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="2"/>
@@ -4154,7 +5609,7 @@
   </r>
   <r>
     <n v="4"/>
-    <d v="2023-10-15T00:00:00"/>
+    <x v="5"/>
     <s v="West"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4167,7 +5622,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2023-10-16T00:00:00"/>
+    <x v="6"/>
     <s v="South"/>
     <s v="John Doe"/>
     <x v="3"/>
@@ -4180,7 +5635,7 @@
   </r>
   <r>
     <n v="17"/>
-    <d v="2023-10-16T00:00:00"/>
+    <x v="6"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4193,7 +5648,7 @@
   </r>
   <r>
     <n v="53"/>
-    <d v="2023-10-17T00:00:00"/>
+    <x v="7"/>
     <s v="East"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4206,7 +5661,7 @@
   </r>
   <r>
     <n v="76"/>
-    <d v="2023-10-18T00:00:00"/>
+    <x v="8"/>
     <s v="North"/>
     <s v="John Doe"/>
     <x v="0"/>
@@ -4219,7 +5674,7 @@
   </r>
   <r>
     <n v="9"/>
-    <d v="2023-10-18T00:00:00"/>
+    <x v="8"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -4232,7 +5687,7 @@
   </r>
   <r>
     <n v="40"/>
-    <d v="2023-10-22T00:00:00"/>
+    <x v="9"/>
     <s v="East"/>
     <s v="Laura Black"/>
     <x v="1"/>
@@ -4245,7 +5700,7 @@
   </r>
   <r>
     <n v="47"/>
-    <d v="2023-10-29T00:00:00"/>
+    <x v="10"/>
     <s v="East"/>
     <s v="Mike Brown"/>
     <x v="1"/>
@@ -4258,7 +5713,7 @@
   </r>
   <r>
     <n v="36"/>
-    <d v="2023-10-31T00:00:00"/>
+    <x v="11"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="2"/>
@@ -4271,7 +5726,7 @@
   </r>
   <r>
     <n v="115"/>
-    <d v="2023-11-02T00:00:00"/>
+    <x v="12"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -4284,7 +5739,7 @@
   </r>
   <r>
     <n v="70"/>
-    <d v="2023-11-02T00:00:00"/>
+    <x v="12"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -4297,7 +5752,7 @@
   </r>
   <r>
     <n v="114"/>
-    <d v="2023-11-03T00:00:00"/>
+    <x v="13"/>
     <s v="North"/>
     <s v="Mike Brown"/>
     <x v="1"/>
@@ -4310,7 +5765,7 @@
   </r>
   <r>
     <n v="50"/>
-    <d v="2023-11-04T00:00:00"/>
+    <x v="14"/>
     <s v="North"/>
     <s v="John Doe"/>
     <x v="3"/>
@@ -4323,7 +5778,7 @@
   </r>
   <r>
     <n v="25"/>
-    <d v="2023-11-05T00:00:00"/>
+    <x v="15"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -4336,7 +5791,7 @@
   </r>
   <r>
     <n v="116"/>
-    <d v="2023-11-10T00:00:00"/>
+    <x v="16"/>
     <s v="North"/>
     <s v="Andrew Blue"/>
     <x v="3"/>
@@ -4349,7 +5804,7 @@
   </r>
   <r>
     <n v="104"/>
-    <d v="2023-11-13T00:00:00"/>
+    <x v="17"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4362,7 +5817,7 @@
   </r>
   <r>
     <n v="67"/>
-    <d v="2023-11-19T00:00:00"/>
+    <x v="18"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -4375,7 +5830,7 @@
   </r>
   <r>
     <n v="34"/>
-    <d v="2023-11-21T00:00:00"/>
+    <x v="19"/>
     <s v="West"/>
     <s v="David White"/>
     <x v="2"/>
@@ -4388,7 +5843,7 @@
   </r>
   <r>
     <n v="43"/>
-    <d v="2023-11-22T00:00:00"/>
+    <x v="20"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4401,7 +5856,7 @@
   </r>
   <r>
     <n v="83"/>
-    <d v="2023-11-24T00:00:00"/>
+    <x v="21"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="2"/>
@@ -4414,7 +5869,7 @@
   </r>
   <r>
     <n v="20"/>
-    <d v="2023-11-24T00:00:00"/>
+    <x v="21"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -4427,7 +5882,7 @@
   </r>
   <r>
     <n v="109"/>
-    <d v="2023-11-26T00:00:00"/>
+    <x v="22"/>
     <s v="East"/>
     <s v="David White"/>
     <x v="1"/>
@@ -4440,7 +5895,7 @@
   </r>
   <r>
     <n v="108"/>
-    <d v="2023-12-04T00:00:00"/>
+    <x v="23"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4453,7 +5908,7 @@
   </r>
   <r>
     <n v="118"/>
-    <d v="2023-12-13T00:00:00"/>
+    <x v="24"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4466,7 +5921,7 @@
   </r>
   <r>
     <n v="103"/>
-    <d v="2023-12-14T00:00:00"/>
+    <x v="25"/>
     <s v="East"/>
     <s v="Mike Brown"/>
     <x v="1"/>
@@ -4479,7 +5934,7 @@
   </r>
   <r>
     <n v="93"/>
-    <d v="2023-12-17T00:00:00"/>
+    <x v="26"/>
     <s v="South"/>
     <s v="David White"/>
     <x v="1"/>
@@ -4492,7 +5947,7 @@
   </r>
   <r>
     <n v="98"/>
-    <d v="2023-12-22T00:00:00"/>
+    <x v="27"/>
     <s v="West"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4505,7 +5960,7 @@
   </r>
   <r>
     <n v="61"/>
-    <d v="2023-12-26T00:00:00"/>
+    <x v="28"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="1"/>
@@ -4518,7 +5973,7 @@
   </r>
   <r>
     <n v="100"/>
-    <d v="2023-12-26T00:00:00"/>
+    <x v="28"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="0"/>
@@ -4531,7 +5986,7 @@
   </r>
   <r>
     <n v="28"/>
-    <d v="2023-12-26T00:00:00"/>
+    <x v="28"/>
     <s v="West"/>
     <s v="Mike Brown"/>
     <x v="1"/>
@@ -4544,7 +5999,7 @@
   </r>
   <r>
     <n v="90"/>
-    <d v="2023-12-29T00:00:00"/>
+    <x v="29"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="3"/>
@@ -4557,7 +6012,7 @@
   </r>
   <r>
     <n v="58"/>
-    <d v="2024-01-01T00:00:00"/>
+    <x v="30"/>
     <s v="South"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4570,7 +6025,7 @@
   </r>
   <r>
     <n v="97"/>
-    <d v="2024-01-02T00:00:00"/>
+    <x v="31"/>
     <s v="West"/>
     <s v="John Doe"/>
     <x v="0"/>
@@ -4583,7 +6038,7 @@
   </r>
   <r>
     <n v="22"/>
-    <d v="2024-01-03T00:00:00"/>
+    <x v="32"/>
     <s v="West"/>
     <s v="Chris Green"/>
     <x v="2"/>
@@ -4596,7 +6051,7 @@
   </r>
   <r>
     <n v="57"/>
-    <d v="2024-01-05T00:00:00"/>
+    <x v="33"/>
     <s v="West"/>
     <s v="John Doe"/>
     <x v="3"/>
@@ -4609,7 +6064,7 @@
   </r>
   <r>
     <n v="24"/>
-    <d v="2024-01-05T00:00:00"/>
+    <x v="33"/>
     <s v="South"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4622,7 +6077,7 @@
   </r>
   <r>
     <n v="8"/>
-    <d v="2024-01-08T00:00:00"/>
+    <x v="34"/>
     <s v="West"/>
     <s v="David White"/>
     <x v="0"/>
@@ -4635,7 +6090,7 @@
   </r>
   <r>
     <n v="21"/>
-    <d v="2024-01-13T00:00:00"/>
+    <x v="35"/>
     <s v="South"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4648,7 +6103,7 @@
   </r>
   <r>
     <n v="88"/>
-    <d v="2024-01-14T00:00:00"/>
+    <x v="36"/>
     <s v="North"/>
     <s v="Andrew Blue"/>
     <x v="3"/>
@@ -4661,7 +6116,7 @@
   </r>
   <r>
     <n v="119"/>
-    <d v="2024-01-14T00:00:00"/>
+    <x v="36"/>
     <s v="West"/>
     <s v="Mike Brown"/>
     <x v="0"/>
@@ -4674,7 +6129,7 @@
   </r>
   <r>
     <n v="86"/>
-    <d v="2024-01-16T00:00:00"/>
+    <x v="37"/>
     <s v="South"/>
     <s v="Andrew Blue"/>
     <x v="1"/>
@@ -4687,7 +6142,7 @@
   </r>
   <r>
     <n v="85"/>
-    <d v="2024-01-18T00:00:00"/>
+    <x v="38"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -4700,7 +6155,7 @@
   </r>
   <r>
     <n v="16"/>
-    <d v="2024-01-27T00:00:00"/>
+    <x v="39"/>
     <s v="North"/>
     <s v="Jane Smith"/>
     <x v="3"/>
@@ -4713,7 +6168,7 @@
   </r>
   <r>
     <n v="92"/>
-    <d v="2024-02-07T00:00:00"/>
+    <x v="40"/>
     <s v="South"/>
     <s v="John Doe"/>
     <x v="2"/>
@@ -4726,7 +6181,7 @@
   </r>
   <r>
     <n v="87"/>
-    <d v="2024-02-08T00:00:00"/>
+    <x v="41"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -4739,7 +6194,7 @@
   </r>
   <r>
     <n v="11"/>
-    <d v="2024-02-13T00:00:00"/>
+    <x v="42"/>
     <s v="West"/>
     <s v="Emily Davis"/>
     <x v="2"/>
@@ -4752,7 +6207,7 @@
   </r>
   <r>
     <n v="81"/>
-    <d v="2024-02-13T00:00:00"/>
+    <x v="42"/>
     <s v="East"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4765,7 +6220,7 @@
   </r>
   <r>
     <n v="29"/>
-    <d v="2024-02-17T00:00:00"/>
+    <x v="43"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -4778,7 +6233,7 @@
   </r>
   <r>
     <n v="96"/>
-    <d v="2024-02-25T00:00:00"/>
+    <x v="44"/>
     <s v="North"/>
     <s v="Andrew Blue"/>
     <x v="1"/>
@@ -4791,7 +6246,7 @@
   </r>
   <r>
     <n v="89"/>
-    <d v="2024-02-26T00:00:00"/>
+    <x v="45"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="0"/>
@@ -4804,7 +6259,7 @@
   </r>
   <r>
     <n v="68"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="South"/>
     <s v="Chris Green"/>
     <x v="1"/>
@@ -4817,7 +6272,7 @@
   </r>
   <r>
     <n v="71"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="North"/>
     <s v="Chris Green"/>
     <x v="3"/>
@@ -4830,7 +6285,7 @@
   </r>
   <r>
     <n v="6"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="West"/>
     <s v="Jane Smith"/>
     <x v="2"/>
@@ -4843,7 +6298,7 @@
   </r>
   <r>
     <n v="49"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="South"/>
     <s v="Jane Smith"/>
     <x v="2"/>
@@ -4856,7 +6311,7 @@
   </r>
   <r>
     <n v="62"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="West"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4869,7 +6324,7 @@
   </r>
   <r>
     <n v="80"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="South"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4882,7 +6337,7 @@
   </r>
   <r>
     <n v="52"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="South"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4895,7 +6350,7 @@
   </r>
   <r>
     <n v="105"/>
-    <d v="2024-02-28T00:00:00"/>
+    <x v="46"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -4908,7 +6363,7 @@
   </r>
   <r>
     <n v="72"/>
-    <d v="2024-03-05T00:00:00"/>
+    <x v="47"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -4921,7 +6376,7 @@
   </r>
   <r>
     <n v="75"/>
-    <d v="2024-03-06T00:00:00"/>
+    <x v="48"/>
     <s v="West"/>
     <s v="David White"/>
     <x v="1"/>
@@ -4934,7 +6389,7 @@
   </r>
   <r>
     <n v="120"/>
-    <d v="2024-03-10T00:00:00"/>
+    <x v="49"/>
     <s v="East"/>
     <s v="Sarah Lee"/>
     <x v="1"/>
@@ -4947,7 +6402,7 @@
   </r>
   <r>
     <n v="51"/>
-    <d v="2024-03-13T00:00:00"/>
+    <x v="50"/>
     <s v="South"/>
     <s v="Mike Brown"/>
     <x v="2"/>
@@ -4960,7 +6415,7 @@
   </r>
   <r>
     <n v="84"/>
-    <d v="2024-03-18T00:00:00"/>
+    <x v="51"/>
     <s v="West"/>
     <s v="Andrew Blue"/>
     <x v="0"/>
@@ -4973,7 +6428,7 @@
   </r>
   <r>
     <n v="113"/>
-    <d v="2024-03-19T00:00:00"/>
+    <x v="52"/>
     <s v="East"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -4986,7 +6441,7 @@
   </r>
   <r>
     <n v="32"/>
-    <d v="2024-03-20T00:00:00"/>
+    <x v="53"/>
     <s v="East"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -4999,7 +6454,7 @@
   </r>
   <r>
     <n v="60"/>
-    <d v="2024-03-21T00:00:00"/>
+    <x v="54"/>
     <s v="North"/>
     <s v="John Doe"/>
     <x v="2"/>
@@ -5012,7 +6467,7 @@
   </r>
   <r>
     <n v="117"/>
-    <d v="2024-03-23T00:00:00"/>
+    <x v="55"/>
     <s v="North"/>
     <s v="Jane Smith"/>
     <x v="0"/>
@@ -5025,7 +6480,7 @@
   </r>
   <r>
     <n v="37"/>
-    <d v="2024-03-26T00:00:00"/>
+    <x v="56"/>
     <s v="North"/>
     <s v="Chris Green"/>
     <x v="1"/>
@@ -5038,7 +6493,7 @@
   </r>
   <r>
     <n v="65"/>
-    <d v="2024-03-27T00:00:00"/>
+    <x v="57"/>
     <s v="East"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5051,7 +6506,7 @@
   </r>
   <r>
     <n v="1"/>
-    <d v="2024-03-29T00:00:00"/>
+    <x v="58"/>
     <s v="South"/>
     <s v="John Doe"/>
     <x v="1"/>
@@ -5064,7 +6519,7 @@
   </r>
   <r>
     <n v="18"/>
-    <d v="2024-03-30T00:00:00"/>
+    <x v="59"/>
     <s v="West"/>
     <s v="Chris Green"/>
     <x v="1"/>
@@ -5077,7 +6532,7 @@
   </r>
   <r>
     <n v="110"/>
-    <d v="2024-04-01T00:00:00"/>
+    <x v="60"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="2"/>
@@ -5090,7 +6545,7 @@
   </r>
   <r>
     <n v="66"/>
-    <d v="2024-04-08T00:00:00"/>
+    <x v="61"/>
     <s v="West"/>
     <s v="Andrew Blue"/>
     <x v="0"/>
@@ -5103,7 +6558,7 @@
   </r>
   <r>
     <n v="106"/>
-    <d v="2024-04-10T00:00:00"/>
+    <x v="62"/>
     <s v="South"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5116,7 +6571,7 @@
   </r>
   <r>
     <n v="15"/>
-    <d v="2024-04-16T00:00:00"/>
+    <x v="63"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5129,7 +6584,7 @@
   </r>
   <r>
     <n v="41"/>
-    <d v="2024-04-25T00:00:00"/>
+    <x v="64"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -5142,7 +6597,7 @@
   </r>
   <r>
     <n v="12"/>
-    <d v="2024-04-28T00:00:00"/>
+    <x v="65"/>
     <s v="West"/>
     <s v="Emily Davis"/>
     <x v="1"/>
@@ -5155,7 +6610,7 @@
   </r>
   <r>
     <n v="107"/>
-    <d v="2024-04-30T00:00:00"/>
+    <x v="66"/>
     <s v="East"/>
     <s v="Andrew Blue"/>
     <x v="2"/>
@@ -5168,7 +6623,7 @@
   </r>
   <r>
     <n v="2"/>
-    <d v="2024-05-08T00:00:00"/>
+    <x v="67"/>
     <s v="West"/>
     <s v="Laura Black"/>
     <x v="3"/>
@@ -5181,7 +6636,7 @@
   </r>
   <r>
     <n v="33"/>
-    <d v="2024-05-10T00:00:00"/>
+    <x v="68"/>
     <s v="East"/>
     <s v="Emily Davis"/>
     <x v="0"/>
@@ -5194,7 +6649,7 @@
   </r>
   <r>
     <n v="42"/>
-    <d v="2024-05-12T00:00:00"/>
+    <x v="69"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5207,7 +6662,7 @@
   </r>
   <r>
     <n v="94"/>
-    <d v="2024-05-15T00:00:00"/>
+    <x v="70"/>
     <s v="North"/>
     <s v="Emily Davis"/>
     <x v="1"/>
@@ -5220,7 +6675,7 @@
   </r>
   <r>
     <n v="64"/>
-    <d v="2024-05-20T00:00:00"/>
+    <x v="71"/>
     <s v="West"/>
     <s v="John Doe"/>
     <x v="0"/>
@@ -5233,7 +6688,7 @@
   </r>
   <r>
     <n v="91"/>
-    <d v="2024-06-01T00:00:00"/>
+    <x v="72"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -5246,7 +6701,7 @@
   </r>
   <r>
     <n v="5"/>
-    <d v="2024-06-06T00:00:00"/>
+    <x v="73"/>
     <s v="South"/>
     <s v="Jane Smith"/>
     <x v="2"/>
@@ -5259,7 +6714,7 @@
   </r>
   <r>
     <n v="44"/>
-    <d v="2024-06-08T00:00:00"/>
+    <x v="74"/>
     <s v="East"/>
     <s v="Laura Black"/>
     <x v="3"/>
@@ -5272,7 +6727,7 @@
   </r>
   <r>
     <n v="59"/>
-    <d v="2024-06-10T00:00:00"/>
+    <x v="75"/>
     <s v="North"/>
     <s v="John Doe"/>
     <x v="0"/>
@@ -5285,7 +6740,7 @@
   </r>
   <r>
     <n v="82"/>
-    <d v="2024-06-14T00:00:00"/>
+    <x v="76"/>
     <s v="East"/>
     <s v="John Doe"/>
     <x v="3"/>
@@ -5298,7 +6753,7 @@
   </r>
   <r>
     <n v="45"/>
-    <d v="2024-06-15T00:00:00"/>
+    <x v="77"/>
     <s v="West"/>
     <s v="Sarah Lee"/>
     <x v="0"/>
@@ -5311,7 +6766,7 @@
   </r>
   <r>
     <n v="99"/>
-    <d v="2024-06-21T00:00:00"/>
+    <x v="78"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -5324,7 +6779,7 @@
   </r>
   <r>
     <n v="14"/>
-    <d v="2024-06-22T00:00:00"/>
+    <x v="79"/>
     <s v="South"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -5337,7 +6792,7 @@
   </r>
   <r>
     <n v="38"/>
-    <d v="2024-06-24T00:00:00"/>
+    <x v="80"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -5350,7 +6805,7 @@
   </r>
   <r>
     <n v="19"/>
-    <d v="2024-06-26T00:00:00"/>
+    <x v="81"/>
     <s v="West"/>
     <s v="Chris Green"/>
     <x v="1"/>
@@ -5363,7 +6818,7 @@
   </r>
   <r>
     <n v="78"/>
-    <d v="2024-06-26T00:00:00"/>
+    <x v="81"/>
     <s v="South"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -5376,7 +6831,7 @@
   </r>
   <r>
     <n v="7"/>
-    <d v="2024-06-29T00:00:00"/>
+    <x v="82"/>
     <s v="West"/>
     <s v="Andrew Blue"/>
     <x v="2"/>
@@ -5389,7 +6844,7 @@
   </r>
   <r>
     <n v="13"/>
-    <d v="2024-06-29T00:00:00"/>
+    <x v="82"/>
     <s v="North"/>
     <s v="John Doe"/>
     <x v="0"/>
@@ -5402,7 +6857,7 @@
   </r>
   <r>
     <n v="77"/>
-    <d v="2024-07-05T00:00:00"/>
+    <x v="83"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -5415,7 +6870,7 @@
   </r>
   <r>
     <n v="39"/>
-    <d v="2024-07-16T00:00:00"/>
+    <x v="84"/>
     <s v="North"/>
     <s v="Sarah Lee"/>
     <x v="1"/>
@@ -5428,7 +6883,7 @@
   </r>
   <r>
     <n v="102"/>
-    <d v="2024-07-24T00:00:00"/>
+    <x v="85"/>
     <s v="East"/>
     <s v="Jane Smith"/>
     <x v="1"/>
@@ -5441,7 +6896,7 @@
   </r>
   <r>
     <n v="111"/>
-    <d v="2024-07-24T00:00:00"/>
+    <x v="85"/>
     <s v="North"/>
     <s v="Jane Smith"/>
     <x v="0"/>
@@ -5454,7 +6909,7 @@
   </r>
   <r>
     <n v="3"/>
-    <d v="2024-07-31T00:00:00"/>
+    <x v="86"/>
     <s v="North"/>
     <s v="Sarah Lee"/>
     <x v="2"/>
@@ -5467,7 +6922,7 @@
   </r>
   <r>
     <n v="73"/>
-    <d v="2024-08-02T00:00:00"/>
+    <x v="87"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -5480,7 +6935,7 @@
   </r>
   <r>
     <n v="10"/>
-    <d v="2024-08-04T00:00:00"/>
+    <x v="88"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5493,7 +6948,7 @@
   </r>
   <r>
     <n v="54"/>
-    <d v="2024-08-06T00:00:00"/>
+    <x v="89"/>
     <s v="West"/>
     <s v="David White"/>
     <x v="1"/>
@@ -5506,7 +6961,7 @@
   </r>
   <r>
     <n v="63"/>
-    <d v="2024-08-06T00:00:00"/>
+    <x v="89"/>
     <s v="East"/>
     <s v="John Doe"/>
     <x v="1"/>
@@ -5519,7 +6974,7 @@
   </r>
   <r>
     <n v="27"/>
-    <d v="2024-08-07T00:00:00"/>
+    <x v="90"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -5532,7 +6987,7 @@
   </r>
   <r>
     <n v="23"/>
-    <d v="2024-08-16T00:00:00"/>
+    <x v="91"/>
     <s v="North"/>
     <s v="Andrew Blue"/>
     <x v="1"/>
@@ -5545,7 +7000,7 @@
   </r>
   <r>
     <n v="95"/>
-    <d v="2024-08-17T00:00:00"/>
+    <x v="92"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -5558,7 +7013,7 @@
   </r>
   <r>
     <n v="112"/>
-    <d v="2024-08-23T00:00:00"/>
+    <x v="93"/>
     <s v="East"/>
     <s v="Emily Davis"/>
     <x v="1"/>
@@ -5571,7 +7026,7 @@
   </r>
   <r>
     <n v="26"/>
-    <d v="2024-08-26T00:00:00"/>
+    <x v="94"/>
     <s v="West"/>
     <s v="Nancy Grey"/>
     <x v="1"/>
@@ -5584,7 +7039,7 @@
   </r>
   <r>
     <n v="69"/>
-    <d v="2024-08-28T00:00:00"/>
+    <x v="95"/>
     <s v="East"/>
     <s v="Sarah Lee"/>
     <x v="3"/>
@@ -5597,7 +7052,7 @@
   </r>
   <r>
     <n v="31"/>
-    <d v="2024-09-08T00:00:00"/>
+    <x v="96"/>
     <s v="North"/>
     <s v="Nancy Grey"/>
     <x v="0"/>
@@ -5610,7 +7065,7 @@
   </r>
   <r>
     <n v="79"/>
-    <d v="2024-09-09T00:00:00"/>
+    <x v="97"/>
     <s v="East"/>
     <s v="Nancy Grey"/>
     <x v="2"/>
@@ -5623,7 +7078,7 @@
   </r>
   <r>
     <n v="55"/>
-    <d v="2024-09-14T00:00:00"/>
+    <x v="98"/>
     <s v="South"/>
     <s v="Nancy Grey"/>
     <x v="3"/>
@@ -5638,7 +7093,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B35CA05-A3F7-4C41-8EFA-000B7C4E52D9}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B35CA05-A3F7-4C41-8EFA-000B7C4E52D9}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0"/>
@@ -5708,10 +7163,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Number of tasks by Managers" fld="0" subtotal="count" baseField="3" baseItem="0" numFmtId="165"/>
+    <dataField name="Number of tasks by Managers" fld="0" subtotal="count" baseField="3" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="8">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -5739,11 +7194,114 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C9B7D1A6-DF1C-449E-8D17-D1C2BA0794F5}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C9B7D1A6-DF1C-449E-8D17-D1C2BA0794F5}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
+  <pivotFields count="14">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="100">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -5761,6 +7319,45 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -5786,10 +7383,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Production cost by product type" fld="6" baseField="4" baseItem="1" numFmtId="165"/>
+    <dataField name="Total Production cost by product type" fld="6" baseField="4" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -5799,6 +7396,277 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1197F0EE-12CE-458C-B000-2BD2B4CD62D8}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="100">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item sd="0" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="13"/>
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of UnitsProduced" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -6252,6 +8120,157 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B97F49-75AB-409C-8A5F-3699A3FD24EA}">
+  <dimension ref="A3:B19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="8">
+        <v>11171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="8">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="8">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="8">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="8">
+        <v>23556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="8">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="8">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="8">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="8">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="8">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="8">
+        <v>34727</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
